--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_25-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_25-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9079B166-F3F9-4779-83D7-0A5235466ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88987FBB-C671-40E4-8043-D3A37856BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30795" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2065,7 +2065,7 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>86</v>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_25-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_25-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88987FBB-C671-40E4-8043-D3A37856BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DFF235-4007-4AED-853F-BC49F9276B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="259">
   <si>
     <t>SKU</t>
   </si>
@@ -791,6 +791,12 @@
   </si>
   <si>
     <t>£57.57</t>
+  </si>
+  <si>
+    <t>£35.53</t>
+  </si>
+  <si>
+    <t>£40.65</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1585,7 @@
         <v>113</v>
       </c>
       <c r="I8" t="s">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="J8" t="s">
         <v>229</v>
@@ -1635,7 +1641,7 @@
         <v>114</v>
       </c>
       <c r="I9" t="s">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="J9" t="s">
         <v>138</v>
